--- a/Result/profitability/6994.xlsx
+++ b/Result/profitability/6994.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM16"/>
+  <dimension ref="A1:AM17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1978,11 +1978,11 @@
         <v>14.2</v>
       </c>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6.88%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -2105,15 +2105,15 @@
         <v>19.92</v>
       </c>
       <c r="G14" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>11.68%</t>
+          <t>11.61%</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="J14" t="n">
         <v>50</v>
@@ -2460,6 +2460,133 @@
       </c>
       <c r="AM16" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6994</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>579</v>
+      </c>
+      <c r="D17" t="n">
+        <v>529</v>
+      </c>
+      <c r="E17" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-1.87%</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>-28</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-39</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-41</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.88125</v>
+      </c>
+      <c r="N17" t="n">
+        <v>17.9525</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-2.166666666666667</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.552371026576342</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.8200000000000001</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-3.153846153846154</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-5.609999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.3950704225352113</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK17" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
